--- a/工作/20260425/银行存款.xlsx
+++ b/工作/20260425/银行存款.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\learnPython\project\工作\20260425\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C1021B5-3394-475E-8483-DB3CDEB601D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F690464-B689-433E-86BE-09A034B60772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="18000" windowHeight="10433" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="银行存款" sheetId="1" r:id="rId1"/>
